--- a/Output/AllModels_MainModels_3_level12000.xlsx
+++ b/Output/AllModels_MainModels_3_level12000.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="264">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">[29.77, 41.53]</t>
   </si>
   <si>
-    <t xml:space="preserve">110.30***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[99.45, 122.42]</t>
+    <t xml:space="preserve">110.25***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[99.57, 122.35]</t>
   </si>
   <si>
     <t xml:space="preserve">3.66***</t>
@@ -398,13 +398,13 @@
     <t xml:space="preserve">1.15</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 0.81,   1.61]</t>
+    <t xml:space="preserve">[ 0.82,   1.61]</t>
   </si>
   <si>
     <t xml:space="preserve">0.36</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.35, 1.07]</t>
+    <t xml:space="preserve">[-0.36, 1.08]</t>
   </si>
   <si>
     <t xml:space="preserve">2.03</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">[ 0.62,  1.26]</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 0.70,   1.43]</t>
+    <t xml:space="preserve">[ 0.69,   1.43]</t>
   </si>
   <si>
     <t xml:space="preserve">0.27</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.44, 0.99]</t>
+    <t xml:space="preserve">[-0.45, 0.99]</t>
   </si>
   <si>
     <t xml:space="preserve">2.35</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">0.92</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 0.58,   1.45]</t>
+    <t xml:space="preserve">[ 0.58,   1.46]</t>
   </si>
   <si>
     <t xml:space="preserve">-0.35</t>
   </si>
   <si>
-    <t xml:space="preserve">[-1.30, 0.58]</t>
+    <t xml:space="preserve">[-1.29, 0.59]</t>
   </si>
   <si>
     <t xml:space="preserve">30.90*</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">[ 0.26,  1.45]</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 0.63,   1.53]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.28, 0.60]</t>
+    <t xml:space="preserve">[ 0.64,   1.53]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-1.29, 0.61]</t>
   </si>
   <si>
     <t xml:space="preserve">2.05</t>
@@ -518,16 +518,13 @@
     <t xml:space="preserve">[ 0.79,  2.97]</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.56,   1.65]</t>
+    <t xml:space="preserve">[ 0.57,   1.64]</t>
   </si>
   <si>
     <t xml:space="preserve">0.22</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.88, 1.35]</t>
+    <t xml:space="preserve">[-0.88, 1.34]</t>
   </si>
   <si>
     <t xml:space="preserve">[0.04,  19.96]</t>
@@ -551,13 +548,13 @@
     <t xml:space="preserve">1.22</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 0.72,   2.08]</t>
+    <t xml:space="preserve">[ 0.71,   2.09]</t>
   </si>
   <si>
     <t xml:space="preserve">0.32</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.81, 1.42]</t>
+    <t xml:space="preserve">[-0.80, 1.44]</t>
   </si>
   <si>
     <t xml:space="preserve">0.05*</t>
@@ -590,7 +587,7 @@
     <t xml:space="preserve">0.21</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.06, 0.33]</t>
+    <t xml:space="preserve">[0.06, 0.32]</t>
   </si>
   <si>
     <t xml:space="preserve">0.41</t>
@@ -728,7 +725,7 @@
     <t xml:space="preserve">[0.02, 0.18]</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.01, 0.16]</t>
+    <t xml:space="preserve">[0.02, 0.16]</t>
   </si>
   <si>
     <t xml:space="preserve">[0.00, 0.16]</t>
@@ -1883,62 +1880,62 @@
         <v>167</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>37</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="K22" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1957,412 +1954,412 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>147</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="J26" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="H28" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="I28" s="1" t="s">
+      <c r="J28" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>71</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="I30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="H31" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="I31" s="1" t="s">
+      <c r="J31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>138</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>156</v>
       </c>
       <c r="I33" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="K33" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="F35" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
